--- a/basedatos_partidas/salida/descompuestos/CT-19-02-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-19-02-010.xlsx
@@ -565,10 +565,10 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>6.3</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="13">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>73.90000000000001</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -678,10 +678,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>76</v>
+        <v>79.25</v>
       </c>
       <c r="H18" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="19">
@@ -697,7 +697,7 @@
       </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="5" t="n">
-        <v>76.76000000000001</v>
+        <v>80.04000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-19-02-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-19-02-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 19 Gestión de residuos y limpieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Contenedores y acopio</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
